--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B23EB75-F42B-49F0-AFCE-D54E3E67FD48}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7406A7-090D-4A8C-B410-04AC660316E8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Edition" sheetId="1" r:id="rId1"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId2"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -52,6 +54,12 @@
   </si>
   <si>
     <t>Budget: Focus Area</t>
+  </si>
+  <si>
+    <t>Attachments: Notes</t>
+  </si>
+  <si>
+    <t>Budget: Budget Details</t>
   </si>
 </sst>
 </file>
@@ -424,4 +432,122 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7406A7-090D-4A8C-B410-04AC660316E8}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4A5CA-5F6D-4D0A-99D1-058BCA43344C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -53,13 +53,13 @@
     <t>Negoatiation Initiated</t>
   </si>
   <si>
-    <t>Budget: Focus Area</t>
-  </si>
-  <si>
     <t>Attachments: Notes</t>
   </si>
   <si>
     <t>Budget: Budget Details</t>
+  </si>
+  <si>
+    <t>Overview: Project Information</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
     <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -414,7 +414,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -474,7 +474,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -533,7 +533,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D4A5CA-5F6D-4D0A-99D1-058BCA43344C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F175D881-7C37-41C5-81F7-383654AB8938}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -400,10 +400,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -422,10 +422,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F175D881-7C37-41C5-81F7-383654AB8938}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F497327-FABB-4A3B-823B-7D5FC2F34734}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId2"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId3"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId2"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId3"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId4"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="11">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -435,6 +437,100 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -493,7 +589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F497327-FABB-4A3B-823B-7D5FC2F34734}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A9D039-8841-4FA7-A1A7-DFAF934692A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -380,13 +380,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.53125" customWidth="1"/>
+    <col min="3" max="3" width="25.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -397,7 +397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -408,7 +408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -419,7 +419,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -439,13 +439,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.53125" customWidth="1"/>
+    <col min="3" max="3" width="19.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -467,7 +467,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -486,13 +486,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.53125" customWidth="1"/>
+    <col min="3" max="3" width="19.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -514,7 +514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -533,14 +533,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -562,7 +562,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -573,7 +573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -592,14 +592,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -621,7 +621,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -632,7 +632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A9D039-8841-4FA7-A1A7-DFAF934692A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7E6C43-7C1D-4F03-9B3D-4D8A59F74D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId2"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId3"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId4"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId3"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId4"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId5"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId6"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,19 +64,37 @@
   </si>
   <si>
     <t>Overview: Project Information</t>
+  </si>
+  <si>
+    <t>fieldApplicationSectionsForRevision__c</t>
+  </si>
+  <si>
+    <t>fieldTEXTAREAExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>fieldNegotiationDueDate__c</t>
+  </si>
+  <si>
+    <t>Files: Forms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -97,8 +117,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,13 +401,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.53125" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -397,34 +418,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -437,15 +458,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.53125" customWidth="1"/>
-    <col min="3" max="3" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -456,7 +486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -467,7 +497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -483,16 +513,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.53125" customWidth="1"/>
-    <col min="3" max="3" width="19.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,7 +533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -514,7 +544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -530,17 +560,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -562,7 +592,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -573,7 +603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -589,17 +619,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -621,7 +651,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -632,7 +662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -641,6 +671,65 @@
       </c>
       <c r="C4" t="s">
         <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7E6C43-7C1D-4F03-9B3D-4D8A59F74D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1C25DB-3877-489E-8279-1A028F8ED1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="12">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -64,15 +64,6 @@
   </si>
   <si>
     <t>Overview: Project Information</t>
-  </si>
-  <si>
-    <t>fieldApplicationSectionsForRevision__c</t>
-  </si>
-  <si>
-    <t>fieldTEXTAREAExplanationOfRevisionsNeeded__c</t>
-  </si>
-  <si>
-    <t>fieldNegotiationDueDate__c</t>
   </si>
   <si>
     <t>Files: Forms</t>
@@ -82,19 +73,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF202124"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -117,9 +102,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,8 +406,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -433,8 +417,8 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -444,8 +428,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -703,19 +687,19 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -725,8 +709,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>43707</v>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1C25DB-3877-489E-8279-1A028F8ED1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B1F9C5-6319-40FE-A097-3480F90FAA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="13">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Files: Forms</t>
+  </si>
+  <si>
+    <t>Negotiation Initiated</t>
   </si>
 </sst>
 </file>
@@ -385,13 +388,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -402,7 +405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -413,7 +416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -421,10 +424,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -444,7 +447,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -453,13 +456,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +473,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -481,7 +484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -500,13 +503,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -528,7 +531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -547,14 +550,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -576,7 +579,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -587,7 +590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -606,14 +609,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -635,7 +638,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -646,7 +649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -665,14 +668,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -683,7 +686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -694,7 +697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -702,10 +705,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B1F9C5-6319-40FE-A097-3480F90FAA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137E56A7-1E78-463D-B621-9AA1FDD33012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId2"/>
     <sheet name="App Revision" sheetId="4" r:id="rId3"/>
     <sheet name="Due Date" sheetId="5" r:id="rId4"/>
     <sheet name="Edition1" sheetId="2" r:id="rId5"/>
     <sheet name="Edition2" sheetId="3" r:id="rId6"/>
     <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId8"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -70,19 +72,70 @@
   </si>
   <si>
     <t>Negotiation Initiated</t>
+  </si>
+  <si>
+    <t>fieldQuestion1__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>fieldQuestion2__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion3__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion4__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion5__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion6__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion7__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion8__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion9__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion10__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion11__c</t>
+  </si>
+  <si>
+    <t>fieldAppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>Automation PM</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOnForm__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,8 +158,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,13 +442,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -405,7 +459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -416,7 +470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -427,7 +481,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -446,9 +500,80 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -456,13 +581,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -484,7 +609,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -503,13 +628,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,7 +645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -531,7 +656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -550,14 +675,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,7 +693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -579,7 +704,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -590,7 +715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -609,14 +734,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,7 +752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -638,7 +763,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -649,7 +774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -668,14 +793,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -686,7 +811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -697,7 +822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -708,7 +833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -717,6 +842,199 @@
       </c>
       <c r="C4">
         <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137E56A7-1E78-463D-B621-9AA1FDD33012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217CE20-A2FB-489B-A5A2-752081ABE4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
     <sheet name="Edition1" sheetId="2" r:id="rId5"/>
     <sheet name="Edition2" sheetId="3" r:id="rId6"/>
     <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId8"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId9"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId8"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId9"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -117,6 +118,9 @@
   </si>
   <si>
     <t>fieldSubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>Overview: Application Overview</t>
   </si>
 </sst>
 </file>
@@ -498,6 +502,53 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
@@ -850,6 +901,75 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -993,51 +1113,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4217CE20-A2FB-489B-A5A2-752081ABE4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F82A9-E515-4594-A6FA-67132D084176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="31">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>Overview: Application Overview</t>
+  </si>
+  <si>
+    <t>fieldNegotiationDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldApplicationSectionsForRevision__c</t>
   </si>
 </sst>
 </file>
@@ -866,8 +872,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -888,8 +894,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -957,8 +963,8 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>4</v>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C5">
         <v>43707</v>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1F82A9-E515-4594-A6FA-67132D084176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6604CB12-D3BC-47E1-B7B9-876A393BFDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="15" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="32">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t>fieldApplicationSectionsForRevision__c</t>
+  </si>
+  <si>
+    <t>fieldExplanationOfRevisionsNeeded__c</t>
   </si>
 </sst>
 </file>
@@ -495,8 +498,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -579,8 +582,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -590,8 +593,8 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -601,8 +604,8 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
@@ -612,8 +615,8 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -623,8 +626,8 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>4</v>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C6">
         <v>43707</v>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6604CB12-D3BC-47E1-B7B9-876A393BFDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D999E9DE-3922-4FB9-A33F-3023C1B44CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="15" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="App Revision" sheetId="4" r:id="rId3"/>
     <sheet name="Due Date" sheetId="5" r:id="rId4"/>
     <sheet name="Edition1" sheetId="2" r:id="rId5"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId6"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId6"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId7"/>
     <sheet name="Ed_Over" sheetId="10" r:id="rId8"/>
     <sheet name="Form_prog" sheetId="8" r:id="rId9"/>
     <sheet name="Form_stand" sheetId="9" r:id="rId10"/>
@@ -455,13 +455,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -483,7 +483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -494,7 +494,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -514,13 +514,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -561,13 +561,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -589,7 +589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -622,7 +622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -641,13 +641,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -669,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -688,13 +688,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -716,7 +716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -735,14 +735,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -764,7 +764,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -792,16 +792,75 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,18 +871,77 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -831,10 +949,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -842,7 +960,18 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -850,144 +979,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -998,7 +999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1020,7 +1021,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1031,7 +1032,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1053,7 +1054,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1075,7 +1076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1086,7 +1087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1097,7 +1098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1108,7 +1109,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D999E9DE-3922-4FB9-A33F-3023C1B44CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E694EE7B-7174-446B-8645-8C510C70D368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="Edit_2" sheetId="6" r:id="rId2"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId3"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId5"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId6"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId7"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId8"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId9"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId10"/>
+    <sheet name="Edition_PreApp" sheetId="11" r:id="rId1"/>
+    <sheet name="Edition" sheetId="1" r:id="rId2"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId3"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId4"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId5"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId6"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId8"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId9"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId10"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -130,6 +131,15 @@
   </si>
   <si>
     <t>fieldExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>fieldRevisionDueDate__c</t>
+  </si>
+  <si>
+    <t>Overview Tab: Project Information</t>
+  </si>
+  <si>
+    <t>fieldPreApplicationSectionsforRevision__c</t>
   </si>
 </sst>
 </file>
@@ -453,6 +463,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -511,54 +773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -638,7 +853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -685,7 +900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -732,7 +947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -791,7 +1006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -850,7 +1065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -910,13 +1125,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -977,150 +1192,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E694EE7B-7174-446B-8645-8C510C70D368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC9297E-C343-414F-BCEC-292AB82159FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC9297E-C343-414F-BCEC-292AB82159FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495CBC8A-8C3B-477B-AA80-A1CF35FC332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Edition_PreApp" sheetId="11" r:id="rId1"/>
-    <sheet name="Edition" sheetId="1" r:id="rId2"/>
-    <sheet name="Edit_2" sheetId="6" r:id="rId3"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId4"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId5"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId6"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId8"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId9"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId10"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId11"/>
+    <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
+    <sheet name="Edition_PreApp" sheetId="11" r:id="rId2"/>
+    <sheet name="Edition" sheetId="1" r:id="rId3"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId4"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId5"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId6"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId7"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId8"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId9"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId10"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId11"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="35">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -181,9 +182,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,6 +467,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -521,200 +845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -773,7 +904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -853,7 +984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -900,7 +1031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -947,7 +1078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1006,7 +1137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1065,7 +1196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1123,73 +1254,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6604CB12-D3BC-47E1-B7B9-876A393BFDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5895BC9A-BC63-4E2A-BD92-F23736DF7199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="15" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="120" windowWidth="20355" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495CBC8A-8C3B-477B-AA80-A1CF35FC332B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDA2801-71E9-498E-A4B1-14370DC64891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
     <sheet name="Edition_PreApp" sheetId="11" r:id="rId2"/>
     <sheet name="Edition" sheetId="1" r:id="rId3"/>
     <sheet name="Edit_2" sheetId="6" r:id="rId4"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId5"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId6"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId7"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId8"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId9"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId10"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId11"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId12"/>
+    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId5"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId6"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId7"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId8"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId9"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId10"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId11"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId12"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="36">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -141,6 +142,9 @@
   </si>
   <si>
     <t>fieldPreApplicationSectionsforRevision__c</t>
+  </si>
+  <si>
+    <t>Overview: Primary Place of Performance</t>
   </si>
 </sst>
 </file>
@@ -469,13 +473,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -486,7 +490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -497,7 +501,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -508,7 +512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -525,15 +529,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -555,7 +619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -566,7 +630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -577,7 +641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -593,16 +657,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -613,7 +677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -624,7 +688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -635,7 +699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -646,7 +710,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -657,7 +721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -668,7 +732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -679,7 +743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -690,7 +754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -701,7 +765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -712,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -723,7 +787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -739,16 +803,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -759,7 +823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -770,7 +834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -789,13 +853,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -817,7 +881,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -828,7 +892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -848,13 +912,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -865,7 +929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -876,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -887,7 +951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -907,13 +971,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -924,7 +988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -935,7 +999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -946,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -957,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -968,7 +1032,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -985,15 +1049,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1004,25 +1068,80 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
         <v>43707</v>
       </c>
     </row>
@@ -1032,15 +1151,15 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1051,26 +1170,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -1079,16 +1198,63 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1110,7 +1276,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1137,17 +1303,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1158,7 +1324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1180,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1194,64 +1360,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBDA2801-71E9-498E-A4B1-14370DC64891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16224212-0054-4BAB-85AF-99AEA0A24F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -973,7 +973,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16224212-0054-4BAB-85AF-99AEA0A24F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C055E72-AD01-4259-8C0D-156D4ABDB00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -21,11 +21,12 @@
     <sheet name="App Revision" sheetId="4" r:id="rId6"/>
     <sheet name="Due Date" sheetId="5" r:id="rId7"/>
     <sheet name="Edition1" sheetId="2" r:id="rId8"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId9"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId10"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId11"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId12"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId13"/>
+    <sheet name="Nego_Edit_Notes" sheetId="14" r:id="rId9"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId10"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId11"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId12"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId13"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="37">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -145,6 +146,9 @@
   </si>
   <si>
     <t>Overview: Primary Place of Performance</t>
+  </si>
+  <si>
+    <t>Files and Forms: Notes</t>
   </si>
 </sst>
 </file>
@@ -529,6 +533,65 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -588,7 +651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -657,7 +720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -803,7 +866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1304,13 +1367,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4019BDBC-3FE0-4879-9A83-6BAE7622118A}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -1339,21 +1401,32 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>43707</v>
       </c>
     </row>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C055E72-AD01-4259-8C0D-156D4ABDB00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E5F35-5F51-4DCC-AA6B-1BB31CDDF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -148,7 +148,7 @@
     <t>Overview: Primary Place of Performance</t>
   </si>
   <si>
-    <t>Files and Forms: Notes</t>
+    <t>Files: Notes</t>
   </si>
 </sst>
 </file>
